--- a/cases/AConly_case14_phasectrl.xlsx
+++ b/cases/AConly_case14_phasectrl.xlsx
@@ -1604,7 +1604,7 @@
       </c>
       <c r="V1" s="4" t="inlineStr">
         <is>
-          <t>Shunt Steps</t>
+          <t>Shunt Step Size [Mvar]</t>
         </is>
       </c>
     </row>
@@ -2478,7 +2478,7 @@
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>Ctrl Steps</t>
+          <t>Ctrl Step Size</t>
         </is>
       </c>
     </row>
